--- a/spectral_slope/DS-1W複合音単音.xlsx
+++ b/spectral_slope/DS-1W複合音単音.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\spectral_slope\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87EDC66-4B55-4859-A1A0-0652DF7B3941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F384F8B1-BF6A-4148-A5C5-8F98E64CDC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,61 +38,61 @@
     <t>スペクトル傾斜</t>
   </si>
   <si>
-    <t>DIST=0,TONE=0,LEVEL=0</t>
+    <t>DRIVE=0,TONE=0,LEVEL=0</t>
   </si>
   <si>
-    <t>DIST=0,TONE=0,LEVEL=5</t>
+    <t>DRIVE=0,TONE=0,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=0,TONE=0,LEVEL=10</t>
+    <t>DRIVE=0,TONE=0,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=0,TONE=5,LEVEL=5</t>
+    <t>DRIVE=0,TONE=5,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=0,TONE=5,LEVEL=10</t>
+    <t>DRIVE=0,TONE=5,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=0,TONE=10,LEVEL=5</t>
+    <t>DRIVE=0,TONE=10,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=0,TONE=10,LEVEL=10</t>
+    <t>DRIVE=0,TONE=10,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=5,TONE=0,LEVEL=5</t>
+    <t>DRIVE=5,TONE=0,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=5,TONE=0,LEVEL=10</t>
+    <t>DRIVE=5,TONE=0,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=5,TONE=5,LEVEL=5</t>
+    <t>DRIVE=5,TONE=5,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=5,TONE=5,LEVEL=10</t>
+    <t>DRIVE=5,TONE=5,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=5,TONE=10,LEVEL=5</t>
+    <t>DRIVE=5,TONE=10,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=5,TONE=10,LEVEL=10</t>
+    <t>DRIVE=5,TONE=10,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=10,TONE=0,LEVEL=5</t>
+    <t>DRIVE=10,TONE=0,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=10,TONE=0,LEVEL=10</t>
+    <t>DRIVE=10,TONE=0,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=10,TONE=5,LEVEL=5</t>
+    <t>DRIVE=10,TONE=5,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=10,TONE=5,LEVEL=10</t>
+    <t>DRIVE=10,TONE=5,LEVEL=10</t>
   </si>
   <si>
-    <t>DIST=10,TONE=10,LEVEL=5</t>
+    <t>DRIVE=10,TONE=10,LEVEL=5</t>
   </si>
   <si>
-    <t>DIST=10,TONE=10,LEVEL=10</t>
+    <t>DRIVE=10,TONE=10,LEVEL=10</t>
   </si>
 </sst>
 </file>
@@ -214,7 +214,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=0,TONE=0,LEVEL=10</c:v>
+                  <c:v>DRIVE=0,TONE=0,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -565,7 +565,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=0,TONE=5,LEVEL=10</c:v>
+                  <c:v>DRIVE=0,TONE=5,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -916,7 +916,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=0,TONE=10,LEVEL=10</c:v>
+                  <c:v>DRIVE=0,TONE=10,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1267,7 +1267,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=5,TONE=0,LEVEL=10</c:v>
+                  <c:v>DRIVE=5,TONE=0,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1618,7 +1618,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=5,TONE=5,LEVEL=10</c:v>
+                  <c:v>DRIVE=5,TONE=5,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1969,7 +1969,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=5,TONE=10,LEVEL=10</c:v>
+                  <c:v>DRIVE=5,TONE=10,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2320,7 +2320,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=10,TONE=0,LEVEL=10</c:v>
+                  <c:v>DRIVE=10,TONE=0,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2673,7 +2673,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=10,TONE=5,LEVEL=10</c:v>
+                  <c:v>DRIVE=10,TONE=5,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3026,7 +3026,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=10,TONE=10,LEVEL=10</c:v>
+                  <c:v>DRIVE=10,TONE=10,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3733,7 +3733,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=0,TONE=10,LEVEL=10</c:v>
+                  <c:v>DRIVE=0,TONE=10,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4084,7 +4084,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=5,TONE=10,LEVEL=10</c:v>
+                  <c:v>DRIVE=5,TONE=10,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4435,7 +4435,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=10,TONE=10,LEVEL=10</c:v>
+                  <c:v>DRIVE=10,TONE=10,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4807,7 +4807,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=0,TONE=0,LEVEL=10</c:v>
+                        <c:v>DRIVE=0,TONE=0,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -5178,7 +5178,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=0,TONE=5,LEVEL=10</c:v>
+                        <c:v>DRIVE=0,TONE=5,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -5549,7 +5549,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=5,TONE=0,LEVEL=10</c:v>
+                        <c:v>DRIVE=5,TONE=0,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -5920,7 +5920,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=5,TONE=5,LEVEL=10</c:v>
+                        <c:v>DRIVE=5,TONE=5,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -6291,7 +6291,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=10,TONE=0,LEVEL=10</c:v>
+                        <c:v>DRIVE=10,TONE=0,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -6664,7 +6664,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=10,TONE=5,LEVEL=10</c:v>
+                        <c:v>DRIVE=10,TONE=5,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -7376,7 +7376,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=10,TONE=0,LEVEL=10</c:v>
+                  <c:v>DRIVE=10,TONE=0,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -7732,7 +7732,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=10,TONE=5,LEVEL=10</c:v>
+                  <c:v>DRIVE=10,TONE=5,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -8088,7 +8088,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DIST=10,TONE=10,LEVEL=10</c:v>
+                  <c:v>DRIVE=10,TONE=10,LEVEL=10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8460,7 +8460,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=0,TONE=0,LEVEL=10</c:v>
+                        <c:v>DRIVE=0,TONE=0,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -8831,7 +8831,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=0,TONE=5,LEVEL=10</c:v>
+                        <c:v>DRIVE=0,TONE=5,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -9202,7 +9202,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=0,TONE=10,LEVEL=10</c:v>
+                        <c:v>DRIVE=0,TONE=10,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -9573,7 +9573,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=5,TONE=0,LEVEL=10</c:v>
+                        <c:v>DRIVE=5,TONE=0,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -9944,7 +9944,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=5,TONE=5,LEVEL=10</c:v>
+                        <c:v>DRIVE=5,TONE=5,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -10315,7 +10315,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>DIST=5,TONE=10,LEVEL=10</c:v>
+                        <c:v>DRIVE=5,TONE=10,LEVEL=10</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
